--- a/artfynd/A 21747-2025 artfynd.xlsx
+++ b/artfynd/A 21747-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131250773</v>
+        <v>131250725</v>
       </c>
       <c r="B2" t="n">
-        <v>8454</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476821</v>
+        <v>476823</v>
       </c>
       <c r="R2" t="n">
-        <v>6791702</v>
+        <v>6791699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,11 +779,11 @@
         <v>131250724</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -883,54 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131250740</v>
+        <v>131255227</v>
       </c>
       <c r="B4" t="n">
-        <v>8454</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Lillberget, Dlr</t>
+          <t>Öster Lillberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476823</v>
+        <v>476775</v>
       </c>
       <c r="R4" t="n">
-        <v>6791701</v>
+        <v>6791676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,56 +964,61 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131250725</v>
+        <v>131250740</v>
       </c>
       <c r="B5" t="n">
-        <v>79296</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,7 +1029,7 @@
         <v>476823</v>
       </c>
       <c r="R5" t="n">
-        <v>6791699</v>
+        <v>6791701</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,6 +1086,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131250773</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476821</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6791702</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21747-2025 artfynd.xlsx
+++ b/artfynd/A 21747-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131255227</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250740</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,8 +1218,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>